--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484036_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484036_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8681</v>
+        <v>6.9684</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8731</v>
+        <v>7.3662</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005</v>
+        <v>-0.3978</v>
       </c>
       <c r="G2" t="n">
         <v>6.9329</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4263</v>
+        <v>-0.326</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9238</v>
+        <v>-0.4307</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4975</v>
+        <v>0.1047</v>
       </c>
       <c r="V2" t="n">
         <v>2.1469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3527</v>
+        <v>3.8443</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3961</v>
+        <v>2.7476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9565</v>
+        <v>1.0968</v>
       </c>
       <c r="G3" t="n">
         <v>0.9633</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2182</v>
+        <v>0.7099</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2946</v>
+        <v>0.0568</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5128</v>
+        <v>0.6531</v>
       </c>
       <c r="V3" t="n">
         <v>3.9566</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9943</v>
+        <v>1.7549</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9253</v>
+        <v>-0.2859</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9196</v>
+        <v>2.0408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5004</v>
+        <v>1.1668</v>
       </c>
       <c r="H4" t="n">
-        <v>1.104</v>
+        <v>1.33</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6036</v>
+        <v>-0.1632</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7665</v>
+        <v>0.5869</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6059</v>
+        <v>0.504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1606</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2661</v>
+        <v>0.5799</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4981</v>
+        <v>0.826</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7642</v>
+        <v>-0.2461</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9781</v>
+        <v>0.588</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3119</v>
+        <v>0.1191</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6662</v>
+        <v>0.469</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2777</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.0118</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3091</v>
+        <v>1.2348</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5353</v>
+        <v>-1.1237</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8444</v>
+        <v>2.3585</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1668</v>
+        <v>0.5004</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.104</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1632</v>
+        <v>-0.6036</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5869</v>
+        <v>0.7665</v>
       </c>
       <c r="K5" t="n">
-        <v>0.504</v>
+        <v>0.6059</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829</v>
+        <v>0.1606</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5799</v>
+        <v>-0.2661</v>
       </c>
       <c r="N5" t="n">
-        <v>0.826</v>
+        <v>0.4981</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2461</v>
+        <v>-0.7642</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1423</v>
+        <v>1.2186</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1303</v>
+        <v>0.1135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2726</v>
+        <v>1.1051</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2777</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.0118</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1079</v>
+        <v>0.9444</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7916</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8201</v>
+        <v>1.7359</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6724</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1852</v>
+        <v>1.0217</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.0113</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1171</v>
+        <v>1.0329</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.851</v>
+        <v>-0.4342</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3329</v>
+        <v>-1.1685</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4819</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3732</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8746</v>
+        <v>-0.4577</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8615</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0131</v>
+        <v>0.2394</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2554</v>
+        <v>-1.4391</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8691</v>
+        <v>-1.2772</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3863</v>
+        <v>-0.1619</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6811</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0034</v>
+        <v>-0.187</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1928</v>
+        <v>-0.2153</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1961</v>
+        <v>0.0283</v>
       </c>
       <c r="V8" t="n">
         <v>2.4129</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3403</v>
+        <v>-2.2022</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.778</v>
+        <v>-2.6225</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5623</v>
+        <v>0.4204</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.335</v>
+        <v>-1.3633</v>
       </c>
       <c r="H9" t="n">
-        <v>1.905</v>
+        <v>-0.8918</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.24</v>
+        <v>-0.4715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6503</v>
+        <v>-0.327</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2903</v>
+        <v>-0.3672</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.64</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9853</v>
+        <v>-1.0363</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6146</v>
+        <v>-0.5246</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6</v>
+        <v>-0.5117</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3344</v>
+        <v>-0.0454</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4364</v>
+        <v>-0.3117</v>
       </c>
       <c r="U9" t="n">
-        <v>0.102</v>
+        <v>0.2663</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.591</v>
+        <v>-2.2383</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7869</v>
+        <v>-0.676</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1959</v>
+        <v>-1.5623</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3633</v>
+        <v>-0.335</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8918</v>
+        <v>1.905</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4715</v>
+        <v>-2.24</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.327</v>
+        <v>0.6503</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3672</v>
+        <v>1.2903</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0363</v>
+        <v>-0.9853</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5246</v>
+        <v>0.6146</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5117</v>
+        <v>-1.6</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4342</v>
+        <v>-0.2324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4761</v>
+        <v>-0.3344</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0419</v>
+        <v>0.102</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6401</v>
+        <v>-3.9203</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6905</v>
+        <v>-5.9707</v>
       </c>
       <c r="F11" t="n">
         <v>2.0504</v>
@@ -1312,10 +1312,10 @@
         <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3175</v>
+        <v>0.4024</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0485</v>
+        <v>-0.3287</v>
       </c>
       <c r="U11" t="n">
         <v>0.731</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.954300000000001</v>
+        <v>4.512699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.361</v>
+        <v>-3.8023</v>
       </c>
       <c r="F12" t="n">
-        <v>8.315200000000001</v>
+        <v>8.315199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.4821999999999997</v>
@@ -1363,13 +1363,13 @@
         <v>-10.6556</v>
       </c>
       <c r="J12" t="n">
-        <v>7.042700000000001</v>
+        <v>7.042699999999999</v>
       </c>
       <c r="K12" t="n">
         <v>7.2378</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1949999999999994</v>
+        <v>-0.1949999999999985</v>
       </c>
       <c r="M12" t="n">
         <v>-6.560699999999999</v>
@@ -1390,16 +1390,16 @@
         <v>13.8869</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1334</v>
+        <v>2.6921</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.598400000000001</v>
+        <v>-2.0398</v>
       </c>
       <c r="U12" t="n">
-        <v>4.7319</v>
+        <v>4.7318</v>
       </c>
       <c r="V12" t="n">
-        <v>6.2983</v>
+        <v>6.298299999999999</v>
       </c>
       <c r="W12" t="n">
         <v>10.041</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9146</v>
+        <v>2.185</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3229</v>
+        <v>1.425</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5916</v>
+        <v>0.76</v>
       </c>
       <c r="G13" t="n">
         <v>2.2971</v>
@@ -1468,13 +1468,13 @@
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0635</v>
+        <v>0.2069</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.238</v>
+        <v>-0.136</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1746</v>
+        <v>0.3429</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1206</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7895</v>
+        <v>1.9265</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1289</v>
+        <v>0.639</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6607</v>
+        <v>1.2875</v>
       </c>
       <c r="G14" t="n">
         <v>4.7105</v>
@@ -1546,13 +1546,13 @@
         <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1365</v>
+        <v>0.2735</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5586</v>
+        <v>-1.0485</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6952</v>
+        <v>1.322</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4623</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6869</v>
+        <v>1.7115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0702</v>
+        <v>-0.5419</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6167</v>
+        <v>2.2535</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3418</v>
@@ -1624,13 +1624,13 @@
         <v>2.9758</v>
       </c>
       <c r="S15" t="n">
-        <v>0.419</v>
+        <v>0.4436</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3686</v>
+        <v>-0.2436</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0504</v>
+        <v>0.6872</v>
       </c>
       <c r="V15" t="n">
         <v>1.6178</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9335</v>
+        <v>1.0075</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.073</v>
+        <v>-0.971</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0065</v>
+        <v>1.9785</v>
       </c>
       <c r="G16" t="n">
         <v>0.2745</v>
@@ -1702,13 +1702,13 @@
         <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6252</v>
+        <v>-0.5512</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6744</v>
+        <v>-0.5724</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0492</v>
+        <v>0.0212</v>
       </c>
       <c r="V16" t="n">
         <v>1.0858</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0617</v>
+        <v>-0.0591</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9771</v>
+        <v>1.1474</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0388</v>
+        <v>-1.2065</v>
       </c>
       <c r="G17" t="n">
-        <v>1.374</v>
+        <v>0.2779</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0603</v>
+        <v>-0.2222</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3137</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8087</v>
+        <v>1.3911</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0456</v>
+        <v>0.1008</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7631</v>
+        <v>1.2903</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5653</v>
+        <v>-1.1132</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0147</v>
+        <v>-0.323</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5507</v>
+        <v>-0.7902</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6201</v>
+        <v>-0.1062</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0679</v>
+        <v>-0.2436</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.1374</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9405</v>
+        <v>-2.4129</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3354</v>
+        <v>-0.0624</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1474</v>
+        <v>-1.1812</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4828</v>
+        <v>1.1187</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2779</v>
+        <v>1.374</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2222</v>
+        <v>0.0603</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.3137</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3911</v>
+        <v>0.8087</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1008</v>
+        <v>0.0456</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2903</v>
+        <v>0.7631</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1132</v>
+        <v>0.5653</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.323</v>
+        <v>0.0147</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7902</v>
+        <v>0.5507</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3825</v>
+        <v>0.496</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2436</v>
+        <v>-0.272</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1389</v>
+        <v>0.768</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4129</v>
+        <v>-0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9735</v>
+        <v>-1.7463</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0783</v>
+        <v>-2.4864</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1048</v>
+        <v>0.74</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3162</v>
@@ -1936,13 +1936,13 @@
         <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9358</v>
+        <v>0.163</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1872</v>
+        <v>-0.2209</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7486</v>
+        <v>0.3839</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9899</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3617</v>
+        <v>-1.8644</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0297</v>
+        <v>-1.9368</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.332</v>
+        <v>0.0725</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1859</v>
+        <v>-1.6234</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3888</v>
+        <v>-1.7439</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.5747</v>
+        <v>0.1205</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4905</v>
+        <v>-0.1232</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1102</v>
+        <v>-0.8914</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.6007</v>
+        <v>0.7682</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6953</v>
+        <v>-1.5002</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.8525</v>
       </c>
       <c r="O20" t="n">
-        <v>0.026</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.505</v>
+        <v>0.18</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7537</v>
+        <v>-0.8217</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2487</v>
+        <v>1.0018</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6389</v>
+        <v>-1.9374</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2429</v>
+        <v>-1.8257</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.396</v>
+        <v>-0.1118</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6234</v>
+        <v>-2.1859</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7439</v>
+        <v>2.3888</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1205</v>
+        <v>-4.5747</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1232</v>
+        <v>-1.4905</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8914</v>
+        <v>3.1102</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7682</v>
+        <v>-4.6007</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5002</v>
+        <v>-0.6953</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8525</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5945</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1278</v>
+        <v>-0.5497</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5333</v>
+        <v>0.469</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8097</v>
+        <v>-0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8097</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.031</v>
+        <v>-2.7547</v>
       </c>
       <c r="E22" t="n">
         <v>-2.5837</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4473</v>
+        <v>-0.171</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9488</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0741</v>
+        <v>-0.7978</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6235000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4506</v>
+        <v>-0.1743</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.954299999999999</v>
+        <v>-1.5938</v>
       </c>
       <c r="E23" t="n">
         <v>-8.315300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>5.361</v>
+        <v>6.7214</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4821000000000004</v>
@@ -2221,7 +2221,7 @@
         <v>10.6555</v>
       </c>
       <c r="J23" t="n">
-        <v>6.560699999999999</v>
+        <v>6.560700000000001</v>
       </c>
       <c r="K23" t="n">
         <v>-3.8998</v>
@@ -2233,7 +2233,7 @@
         <v>-7.0428</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.237799999999999</v>
+        <v>-7.2378</v>
       </c>
       <c r="O23" t="n">
         <v>0.1951000000000001</v>
@@ -2248,16 +2248,16 @@
         <v>18.8464</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1334</v>
+        <v>0.2271</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.7317</v>
+        <v>-4.7319</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5985</v>
+        <v>4.959100000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-6.2983</v>
+        <v>-6.298300000000001</v>
       </c>
       <c r="W23" t="n">
         <v>3.7429</v>
